--- a/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,7 +996,6 @@
           <t>Icon_MinerLamp</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1015,6 +1014,237 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>每级增加Q4/Q5/Q6生成权重10（满级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（1级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（2级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（3级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（4级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Equip_Detector</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>探测器</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Icon_Detector</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dig</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>DigProcessSpawnCountBonus_5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>每级增加过程生成坟墓数量+1（满级）</t>
         </is>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
@@ -419,94 +419,94 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>装备ID</t>
+          <t>EquipId</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>装备等级</t>
+          <t>EquipLevel</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>装备名称</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>装备图标</t>
+          <t>IconAssetId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>升下一级经验</t>
+          <t>ExpToNextLevel</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>转化经验值</t>
+          <t>ConvertExpValue</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>装备生效功能</t>
+          <t>EffectDomain</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>装备效果</t>
+          <t>EquipEffect</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>装备描述</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>复合主键之一</t>
+          <t>（待补 SPEC 中文说明）EquipId</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>复合主键之一；从1起</t>
+          <t>（待补 SPEC 中文说明）EquipLevel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>展示名</t>
+          <t>（待补 SPEC 中文说明）DisplayName</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UI图标资源Id</t>
+          <t>（待补 SPEC 中文说明）IconAssetId</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>空或≤0=满级行</t>
+          <t>（待补 SPEC 中文说明）ExpToNextLevel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>再获同Id转入经验</t>
+          <t>（待补 SPEC 中文说明）ConvertExpValue</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dig|SoldierManufacture|Combat</t>
+          <t>（待补 SPEC 中文说明）EffectDomain</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dig: Attr_Value|…</t>
+          <t>（待补 SPEC 中文说明）EquipEffect</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>展示文案</t>
+          <t>（待补 SPEC 中文说明）Description</t>
         </is>
       </c>
     </row>
@@ -766,6 +766,7 @@
           <t>Icon_IronShovel</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>1</t>
@@ -996,6 +997,7 @@
           <t>Icon_MinerLamp</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>1</t>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/主角_装备配置表_Protagonist_ProtagonistEquipmentConfig.xlsx
@@ -419,94 +419,94 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>EquipId</t>
+          <t>装备ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>EquipLevel</t>
+          <t>装备等级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DisplayName</t>
+          <t>装备名称</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>IconAssetId</t>
+          <t>装备图标</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ExpToNextLevel</t>
+          <t>升下一级经验</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ConvertExpValue</t>
+          <t>转化经验值</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>EffectDomain</t>
+          <t>装备生效功能</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>EquipEffect</t>
+          <t>装备效果</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>装备描述</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EquipId</t>
+          <t>复合主键之一</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EquipLevel</t>
+          <t>复合主键之一；从 1 起</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）DisplayName</t>
+          <t>展示名；若启用 i18n 可为 Key</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）IconAssetId</t>
+          <t>UI 图标资源 Id</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）ExpToNextLevel</t>
+          <t>升到 EquipLevel+1 所需；空或 ≤0 → 该行为满级</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）ConvertExpValue</t>
+          <t>再获同 EquipId 时转入的经验</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EffectDomain</t>
+          <t>Dig | SoldierManufacture | Combat；可多值</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）EquipEffect</t>
+          <t>Dig 域与科技 AttributeModifiers 同风格；空=无效果</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）Description</t>
+          <t>展示文案</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,6 @@
           <t>Icon_IronShovel</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>1</t>
@@ -997,7 +996,6 @@
           <t>Icon_MinerLamp</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1228,7 +1226,6 @@
           <t>Icon_Detector</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>1</t>
